--- a/artfynd/A 14855-2024 artfynd.xlsx
+++ b/artfynd/A 14855-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66540000</v>
+        <v>66540031</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547348.1815981097</v>
+        <v>547576</v>
       </c>
       <c r="R2" t="n">
-        <v>7264759.40086707</v>
+        <v>7265038</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,21 +743,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>22409</t>
+          <t>22436</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66547569</v>
+        <v>66540009</v>
       </c>
       <c r="B3" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Girjesliden, Ly lm</t>
+          <t>Gainatjärnarna, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547350.3636256495</v>
+        <v>547322</v>
       </c>
       <c r="R3" t="n">
-        <v>7264727.462796987</v>
+        <v>7264504</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,21 +845,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +861,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>26090</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66540014</v>
+        <v>66540013</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547342.9632273098</v>
+        <v>547328</v>
       </c>
       <c r="R4" t="n">
-        <v>7264466.558266927</v>
+        <v>7264496</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,21 +947,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,7 +963,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>22420</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66540015</v>
+        <v>66540006</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547342.9632273098</v>
+        <v>547350</v>
       </c>
       <c r="R5" t="n">
-        <v>7264466.558266927</v>
+        <v>7264727</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,21 +1049,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,7 +1065,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>22415</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66540017</v>
+        <v>66540000</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547414.7523951069</v>
+        <v>547348</v>
       </c>
       <c r="R6" t="n">
-        <v>7264398.373135821</v>
+        <v>7264759</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1216,21 +1151,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1242,7 +1167,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>22424</t>
+          <t>22409</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1260,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66540004</v>
+        <v>66540007</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547345.2278139235</v>
+        <v>547322</v>
       </c>
       <c r="R7" t="n">
-        <v>7264736.514651748</v>
+        <v>7264504</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1333,21 +1253,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1359,7 +1269,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>22413</t>
+          <t>22416</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1377,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66547574</v>
+        <v>66540010</v>
       </c>
       <c r="B8" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,14 +1318,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Girjesliden, Ly lm</t>
+          <t>Gainatjärnarna, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547327.5141573964</v>
+        <v>547328</v>
       </c>
       <c r="R8" t="n">
-        <v>7264496.207261275</v>
+        <v>7264496</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1450,21 +1355,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1476,7 +1371,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>22419</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1494,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66547572</v>
+        <v>66540015</v>
       </c>
       <c r="B9" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,34 +1400,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Girjesliden, Ly lm</t>
+          <t>Gainatjärnarna, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547322.3915116413</v>
+        <v>547343</v>
       </c>
       <c r="R9" t="n">
-        <v>7264504.429549655</v>
+        <v>7264467</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1567,21 +1457,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1593,7 +1473,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>26093</t>
+          <t>22422</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1611,15 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66540007</v>
+        <v>66540020</v>
       </c>
       <c r="B10" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547322.3915116413</v>
+        <v>547434</v>
       </c>
       <c r="R10" t="n">
-        <v>7264504.429549655</v>
+        <v>7264404</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1684,21 +1559,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1710,7 +1575,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>22416</t>
+          <t>22426</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1728,37 +1593,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66540016</v>
+        <v>66540018</v>
       </c>
       <c r="B11" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>547414.7523951069</v>
+        <v>547415</v>
       </c>
       <c r="R11" t="n">
-        <v>7264398.373135821</v>
+        <v>7264398</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1801,21 +1661,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1827,7 +1677,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>22423</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1845,15 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66547593</v>
+        <v>66540004</v>
       </c>
       <c r="B12" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,34 +1706,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Girjesliden, Ly lm</t>
+          <t>Gainatjärnarna, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>547576.4275007698</v>
+        <v>547345</v>
       </c>
       <c r="R12" t="n">
-        <v>7265038.410355326</v>
+        <v>7264737</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1918,21 +1763,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1944,7 +1779,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>26111</t>
+          <t>22413</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1962,15 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66547580</v>
+        <v>66540008</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,14 +1828,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Girjesliden, Ly lm</t>
+          <t>Gainatjärnarna, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>547395.3347845913</v>
+        <v>547322</v>
       </c>
       <c r="R13" t="n">
-        <v>7264416.329890533</v>
+        <v>7264504</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2035,21 +1865,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2061,7 +1881,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>26099</t>
+          <t>22417</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2079,15 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66547579</v>
+        <v>66540017</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,34 +1910,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Girjesliden, Ly lm</t>
+          <t>Gainatjärnarna, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>547395.3347845913</v>
+        <v>547415</v>
       </c>
       <c r="R14" t="n">
-        <v>7264416.329890533</v>
+        <v>7264398</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2152,21 +1967,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2178,7 +1983,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>26098</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2196,50 +2001,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>66540018</v>
+        <v>66547580</v>
       </c>
       <c r="B15" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gainatjärnarna, Ly lm</t>
+          <t>Girjesliden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>547414.7523951069</v>
+        <v>547395</v>
       </c>
       <c r="R15" t="n">
-        <v>7264398.373135821</v>
+        <v>7264416</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2269,21 +2069,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2295,7 +2085,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>22425</t>
+          <t>26099</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2310,357 +2100,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>66540020</v>
-      </c>
-      <c r="B16" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Gainatjärnarna, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>547433.778183923</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7264404.496894193</v>
-      </c>
-      <c r="S16" t="n">
-        <v>50</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>22426</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>66540013</v>
-      </c>
-      <c r="B17" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>864</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Hypogymnia bitteri</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Gainatjärnarna, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>547327.5141573964</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7264496.207261275</v>
-      </c>
-      <c r="S17" t="n">
-        <v>50</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>22420</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>66547571</v>
-      </c>
-      <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Girjesliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>547322.3915116413</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7264504.429549655</v>
-      </c>
-      <c r="S18" t="n">
-        <v>50</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>26092</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
